--- a/output/2026-10-06_02_Croazia_Međimurska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-06_02_Croazia_Međimurska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore/rappresentante in Croazia di macchine utensili CNC EMAG, CHIRON, STAMA (Germania) e lavatrici industriali LPW. Azienda reale confermata via WebFetch sul sito ufficiale (vist-cnc.com) e via companywall.hr (attiva dal 2002, sede in Industrijska ulica 3, Pribislavec-Čakovec, 7 dipendenti). Telefono confermato da companywall.hr (040363562), coincide con quello fornito; il sito mostra anche un numero alternativo (+385 40 386 320) non usato qui per prudenza.</t>
+          <t>Distributore/rappresentante in Croazia di macchine utensili CNC EMAG, CHIRON, STAMA (Germania) e lavatrici industriali LPW. Azienda reale confermata via WebFetch sul sito ufficiale (vist-cnc.com) e via companywall.hr (attiva dal 2002, sede in Industrijska ulica 3, Pribislavec-Čakovec, 7 dipendenti). Telefono confermato da companywall.hr (040363562), coincide con quello fornito; il sito mostra anche un numero alternativo (+385 40 386 320) non usato qui per prudenza. [DUPLICATO — vedi anche: 2026-10-05_23_Croazia_Međimurska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">

--- a/output/2026-10-06_02_Croazia_Međimurska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-06_02_Croazia_Međimurska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
